--- a/jyx2/Assets/Mods/shendiao/Configs/人物.xlsx
+++ b/jyx2/Assets/Mods/shendiao/Configs/人物.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="160">
   <si>
     <t>LuaConfigGen</t>
   </si>
@@ -271,249 +271,150 @@
     <t>-1</t>
   </si>
   <si>
+    <t>郭靖</t>
+  </si>
+  <si>
+    <t>北侠</t>
+  </si>
+  <si>
+    <t>10,400</t>
+  </si>
+  <si>
+    <t>黄蓉</t>
+  </si>
+  <si>
+    <t>桃花岛主之女</t>
+  </si>
+  <si>
+    <t>10,200</t>
+  </si>
+  <si>
+    <t>赵志敬</t>
+  </si>
+  <si>
+    <t>全真教三代首座</t>
+  </si>
+  <si>
+    <t>20,900</t>
+  </si>
+  <si>
+    <t>孙婆婆</t>
+  </si>
+  <si>
+    <t>古墓派老仆</t>
+  </si>
+  <si>
+    <t>20,800</t>
+  </si>
+  <si>
+    <t>小龙女</t>
+  </si>
+  <si>
+    <t>古墓派掌门</t>
+  </si>
+  <si>
+    <t>20,700</t>
+  </si>
+  <si>
+    <t>柯镇恶</t>
+  </si>
+  <si>
+    <t>江南七怪之首</t>
+  </si>
+  <si>
+    <t>30,100</t>
+  </si>
+  <si>
+    <t>34,1</t>
+  </si>
+  <si>
+    <t>洪七公</t>
+  </si>
+  <si>
+    <t>北丐</t>
+  </si>
+  <si>
+    <t>31,900|32,900|33,900</t>
+  </si>
+  <si>
+    <t>欧阳锋</t>
+  </si>
+  <si>
+    <t>西毒</t>
+  </si>
+  <si>
+    <t>40,900|41,900</t>
+  </si>
+  <si>
+    <t>郭芙</t>
+  </si>
+  <si>
+    <t>郭靖之女</t>
+  </si>
+  <si>
+    <t>42,900</t>
+  </si>
+  <si>
+    <t>武敦儒</t>
+  </si>
+  <si>
+    <t>郭靖弟子</t>
+  </si>
+  <si>
+    <t>42,800</t>
+  </si>
+  <si>
+    <t>鹿清笃</t>
+  </si>
+  <si>
+    <t>全真教弟子</t>
+  </si>
+  <si>
+    <t>60,700|61,900</t>
+  </si>
+  <si>
+    <t>伏格多</t>
+  </si>
+  <si>
+    <t>最终boss</t>
+  </si>
+  <si>
+    <t>62,900</t>
+  </si>
+  <si>
+    <t>将军府士兵</t>
+  </si>
+  <si>
+    <t>61,500</t>
+  </si>
+  <si>
+    <t>61,700</t>
+  </si>
+  <si>
+    <t>蓝隼士兵</t>
+  </si>
+  <si>
+    <t>李莫愁</t>
+  </si>
+  <si>
+    <t>赤练仙子</t>
+  </si>
+  <si>
+    <t>70,500|71,400</t>
+  </si>
+  <si>
+    <t>75,1|76,1</t>
+  </si>
+  <si>
+    <t>曼陀谷弟子</t>
+  </si>
+  <si>
     <t>童四二</t>
   </si>
   <si>
-    <t>郭靖</t>
-  </si>
-  <si>
-    <t>北侠</t>
-  </si>
-  <si>
-    <t>10,400</t>
-  </si>
-  <si>
-    <t>王远</t>
-  </si>
-  <si>
-    <t>黄蓉</t>
-  </si>
-  <si>
-    <t>桃花岛主之女</t>
-  </si>
-  <si>
-    <t>10,200</t>
-  </si>
-  <si>
-    <t>佟雯</t>
-  </si>
-  <si>
-    <t>赵志敬</t>
-  </si>
-  <si>
-    <t>全真教三代首座</t>
-  </si>
-  <si>
-    <t>20,900</t>
-  </si>
-  <si>
-    <t>=D8</t>
-  </si>
-  <si>
-    <t>孙婆婆</t>
-  </si>
-  <si>
-    <t>古墓派老仆</t>
-  </si>
-  <si>
-    <t>20,800</t>
-  </si>
-  <si>
-    <t>=D9</t>
-  </si>
-  <si>
-    <t>小龙女</t>
-  </si>
-  <si>
-    <t>古墓派掌门</t>
-  </si>
-  <si>
-    <t>20,700</t>
-  </si>
-  <si>
-    <t>牛妞妞</t>
-  </si>
-  <si>
-    <t>柯镇恶</t>
-  </si>
-  <si>
-    <t>江南七怪之首</t>
-  </si>
-  <si>
-    <t>30,100</t>
-  </si>
-  <si>
-    <t>34,1</t>
-  </si>
-  <si>
-    <t>=D11</t>
-  </si>
-  <si>
-    <t>洪七公</t>
-  </si>
-  <si>
-    <t>北丐</t>
-  </si>
-  <si>
-    <t>31,900|32,900|33,900</t>
-  </si>
-  <si>
-    <t>=D12</t>
-  </si>
-  <si>
-    <t>欧阳锋</t>
-  </si>
-  <si>
-    <t>西毒</t>
-  </si>
-  <si>
-    <t>40,900|41,900</t>
-  </si>
-  <si>
-    <t>=D13</t>
-  </si>
-  <si>
-    <t>郭芙</t>
-  </si>
-  <si>
-    <t>郭靖之女</t>
-  </si>
-  <si>
-    <t>42,900</t>
-  </si>
-  <si>
-    <t>曼陀谷弟子</t>
-  </si>
-  <si>
-    <t>武敦儒</t>
-  </si>
-  <si>
-    <t>郭靖弟子</t>
-  </si>
-  <si>
-    <t>42,800</t>
-  </si>
-  <si>
-    <t>=D15</t>
-  </si>
-  <si>
-    <t>鹿清笃</t>
-  </si>
-  <si>
-    <t>全真教弟子</t>
-  </si>
-  <si>
-    <t>60,700|61,900</t>
-  </si>
-  <si>
-    <t>何云多</t>
-  </si>
-  <si>
-    <t>伏格多</t>
-  </si>
-  <si>
-    <t>最终boss</t>
-  </si>
-  <si>
-    <t>62,900</t>
-  </si>
-  <si>
-    <t>=D17</t>
-  </si>
-  <si>
-    <t>将军府士兵</t>
-  </si>
-  <si>
-    <t>61,500</t>
-  </si>
-  <si>
-    <t>=D18</t>
-  </si>
-  <si>
-    <t>=D19</t>
-  </si>
-  <si>
-    <t>=D20</t>
-  </si>
-  <si>
-    <t>=D21</t>
-  </si>
-  <si>
-    <t>61,700</t>
-  </si>
-  <si>
-    <t>=D22</t>
-  </si>
-  <si>
-    <t>=D23</t>
-  </si>
-  <si>
-    <t>=D24</t>
-  </si>
-  <si>
-    <t>=D25</t>
-  </si>
-  <si>
-    <t>蓝隼士兵</t>
-  </si>
-  <si>
-    <t>=D26</t>
-  </si>
-  <si>
-    <t>=D27</t>
-  </si>
-  <si>
-    <t>=D28</t>
-  </si>
-  <si>
-    <t>=D29</t>
-  </si>
-  <si>
-    <t>=D30</t>
-  </si>
-  <si>
-    <t>=D31</t>
-  </si>
-  <si>
-    <t>=D32</t>
-  </si>
-  <si>
-    <t>=D33</t>
-  </si>
-  <si>
-    <t>=D34</t>
-  </si>
-  <si>
-    <t>=D35</t>
-  </si>
-  <si>
-    <t>李莫愁</t>
-  </si>
-  <si>
-    <t>赤练仙子</t>
-  </si>
-  <si>
-    <t>70,500|71,400</t>
-  </si>
-  <si>
-    <t>75,1|76,1</t>
-  </si>
-  <si>
-    <t>=D36</t>
-  </si>
-  <si>
-    <t>=D37</t>
-  </si>
-  <si>
-    <t>=D38</t>
-  </si>
-  <si>
     <t>鸽子楼徐谦收留的弟子</t>
   </si>
   <si>
-    <t>=D39</t>
-  </si>
-  <si>
     <t>程英</t>
   </si>
   <si>
@@ -526,9 +427,6 @@
     <t>91,1</t>
   </si>
   <si>
-    <t>=D40</t>
-  </si>
-  <si>
     <t>牛不三</t>
   </si>
   <si>
@@ -538,9 +436,6 @@
     <t>90,800</t>
   </si>
   <si>
-    <t>=D41</t>
-  </si>
-  <si>
     <t>庙祝</t>
   </si>
   <si>
@@ -550,9 +445,6 @@
     <t>30,800</t>
   </si>
   <si>
-    <t>=D42</t>
-  </si>
-  <si>
     <t>孙不二</t>
   </si>
   <si>
@@ -562,115 +454,46 @@
     <t>0,0|120,800</t>
   </si>
   <si>
-    <t>=D43</t>
-  </si>
-  <si>
     <t>野狼</t>
   </si>
   <si>
     <t>140,600</t>
   </si>
   <si>
-    <t>=D44</t>
-  </si>
-  <si>
     <t>140,700</t>
   </si>
   <si>
-    <t>=D45</t>
-  </si>
-  <si>
     <t>140,800</t>
   </si>
   <si>
-    <t>=D46</t>
-  </si>
-  <si>
-    <t>=D47</t>
-  </si>
-  <si>
-    <t>=D48</t>
-  </si>
-  <si>
-    <t>=D49</t>
-  </si>
-  <si>
-    <t>=D50</t>
-  </si>
-  <si>
-    <t>=D51</t>
-  </si>
-  <si>
-    <t>=D52</t>
-  </si>
-  <si>
-    <t>=D53</t>
-  </si>
-  <si>
     <t>黑熊</t>
   </si>
   <si>
     <t>160,500</t>
   </si>
   <si>
-    <t>=D54</t>
-  </si>
-  <si>
     <t>160,600</t>
   </si>
   <si>
-    <t>=D55</t>
-  </si>
-  <si>
     <t>160,800</t>
   </si>
   <si>
-    <t>=D56</t>
-  </si>
-  <si>
     <t>160,700</t>
   </si>
   <si>
-    <t>=D57</t>
-  </si>
-  <si>
-    <t>=D58</t>
-  </si>
-  <si>
     <t>巨型黑熊</t>
   </si>
   <si>
-    <t>=D59</t>
-  </si>
-  <si>
     <t>毒蛇</t>
   </si>
   <si>
     <t>180,600</t>
   </si>
   <si>
-    <t>=D60</t>
-  </si>
-  <si>
-    <t>=D61</t>
-  </si>
-  <si>
-    <t>=D62</t>
-  </si>
-  <si>
-    <t>=D63</t>
-  </si>
-  <si>
-    <t>=D64</t>
-  </si>
-  <si>
     <t>路人乙</t>
   </si>
   <si>
     <t>42,700</t>
-  </si>
-  <si>
-    <t>=D65</t>
   </si>
 </sst>
 </file>
@@ -1480,7 +1303,7 @@
         <v>84</v>
       </c>
       <c r="AQ5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:43">
@@ -1494,10 +1317,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" t="s">
         <v>86</v>
-      </c>
-      <c r="E6" t="s">
-        <v>87</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1602,13 +1425,13 @@
         <v>0</v>
       </c>
       <c r="AN6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AO6" t="s">
         <v>84</v>
       </c>
       <c r="AQ6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:43">
@@ -1622,10 +1445,10 @@
         <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1730,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="AN7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AO7" t="s">
         <v>84</v>
@@ -1739,7 +1562,7 @@
         <v>115</v>
       </c>
       <c r="AQ7" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:43">
@@ -1753,10 +1576,10 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1861,13 +1684,13 @@
         <v>0</v>
       </c>
       <c r="AN8" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="AO8" t="s">
         <v>84</v>
       </c>
       <c r="AQ8" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:43">
@@ -1881,10 +1704,10 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1989,13 +1812,13 @@
         <v>0</v>
       </c>
       <c r="AN9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="AO9" t="s">
         <v>84</v>
       </c>
       <c r="AQ9" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:43">
@@ -2009,10 +1832,10 @@
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -2117,13 +1940,13 @@
         <v>0</v>
       </c>
       <c r="AN10" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="AO10" t="s">
         <v>84</v>
       </c>
       <c r="AQ10" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:43">
@@ -2137,10 +1960,10 @@
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -2245,16 +2068,16 @@
         <v>0</v>
       </c>
       <c r="AN11" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="AO11" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="AP11">
         <v>310</v>
       </c>
       <c r="AQ11" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:43">
@@ -2268,10 +2091,10 @@
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -2376,13 +2199,13 @@
         <v>0</v>
       </c>
       <c r="AN12" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="AO12" t="s">
         <v>84</v>
       </c>
       <c r="AQ12" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:43">
@@ -2396,10 +2219,10 @@
         <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E13" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -2504,13 +2327,13 @@
         <v>0</v>
       </c>
       <c r="AN13" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="AO13" t="s">
         <v>84</v>
       </c>
       <c r="AQ13" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:43">
@@ -2524,10 +2347,10 @@
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="E14" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -2632,13 +2455,13 @@
         <v>0</v>
       </c>
       <c r="AN14" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="AO14" t="s">
         <v>84</v>
       </c>
       <c r="AQ14" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:43">
@@ -2652,10 +2475,10 @@
         <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="E15" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -2760,13 +2583,13 @@
         <v>0</v>
       </c>
       <c r="AN15" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="AO15" t="s">
         <v>84</v>
       </c>
       <c r="AQ15" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:43">
@@ -2780,10 +2603,10 @@
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -2888,13 +2711,13 @@
         <v>0</v>
       </c>
       <c r="AN16" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="AO16" t="s">
         <v>84</v>
       </c>
       <c r="AQ16" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:43">
@@ -2908,10 +2731,10 @@
         <v>5</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="E17" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -3016,13 +2839,13 @@
         <v>0</v>
       </c>
       <c r="AN17" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="AO17" t="s">
         <v>84</v>
       </c>
       <c r="AQ17" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:43">
@@ -3036,10 +2859,10 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -3144,13 +2967,13 @@
         <v>0</v>
       </c>
       <c r="AN18" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="AO18" t="s">
         <v>84</v>
       </c>
       <c r="AQ18" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:43">
@@ -3164,10 +2987,10 @@
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E19" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -3272,13 +3095,13 @@
         <v>0</v>
       </c>
       <c r="AN19" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="AO19" t="s">
         <v>84</v>
       </c>
       <c r="AQ19" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:43">
@@ -3292,10 +3115,10 @@
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E20" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -3400,13 +3223,13 @@
         <v>0</v>
       </c>
       <c r="AN20" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="AO20" t="s">
         <v>84</v>
       </c>
       <c r="AQ20" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:43">
@@ -3420,10 +3243,10 @@
         <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E21" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -3528,13 +3351,13 @@
         <v>0</v>
       </c>
       <c r="AN21" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="AO21" t="s">
         <v>84</v>
       </c>
       <c r="AQ21" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:43">
@@ -3548,10 +3371,10 @@
         <v>4</v>
       </c>
       <c r="D22" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E22" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -3656,13 +3479,13 @@
         <v>0</v>
       </c>
       <c r="AN22" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="AO22" t="s">
         <v>84</v>
       </c>
       <c r="AQ22" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:43">
@@ -3676,10 +3499,10 @@
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E23" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -3784,13 +3607,13 @@
         <v>0</v>
       </c>
       <c r="AN23" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="AO23" t="s">
         <v>84</v>
       </c>
       <c r="AQ23" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:43">
@@ -3804,10 +3627,10 @@
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E24" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -3912,13 +3735,13 @@
         <v>0</v>
       </c>
       <c r="AN24" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="AO24" t="s">
         <v>84</v>
       </c>
       <c r="AQ24" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:43">
@@ -3932,10 +3755,10 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E25" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -4040,13 +3863,13 @@
         <v>0</v>
       </c>
       <c r="AN25" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="AO25" t="s">
         <v>84</v>
       </c>
       <c r="AQ25" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:43">
@@ -4060,10 +3883,10 @@
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="E26" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -4168,13 +3991,13 @@
         <v>0</v>
       </c>
       <c r="AN26" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="AO26" t="s">
         <v>84</v>
       </c>
       <c r="AQ26" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:43">
@@ -4188,10 +4011,10 @@
         <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="E27" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -4296,13 +4119,13 @@
         <v>0</v>
       </c>
       <c r="AN27" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="AO27" t="s">
         <v>84</v>
       </c>
       <c r="AQ27" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:43">
@@ -4316,10 +4139,10 @@
         <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="E28" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -4424,13 +4247,13 @@
         <v>0</v>
       </c>
       <c r="AN28" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="AO28" t="s">
         <v>84</v>
       </c>
       <c r="AQ28" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:43">
@@ -4444,10 +4267,10 @@
         <v>4</v>
       </c>
       <c r="D29" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="E29" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -4552,13 +4375,13 @@
         <v>0</v>
       </c>
       <c r="AN29" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="AO29" t="s">
         <v>84</v>
       </c>
       <c r="AQ29" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:43">
@@ -4572,10 +4395,10 @@
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="E30" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -4680,13 +4503,13 @@
         <v>0</v>
       </c>
       <c r="AN30" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="AO30" t="s">
         <v>84</v>
       </c>
       <c r="AQ30" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:43">
@@ -4700,10 +4523,10 @@
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="E31" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -4808,13 +4631,13 @@
         <v>0</v>
       </c>
       <c r="AN31" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="AO31" t="s">
         <v>84</v>
       </c>
       <c r="AQ31" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" spans="1:43">
@@ -4828,10 +4651,10 @@
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="E32" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -4936,13 +4759,13 @@
         <v>0</v>
       </c>
       <c r="AN32" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="AO32" t="s">
         <v>84</v>
       </c>
       <c r="AQ32" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:43">
@@ -4956,10 +4779,10 @@
         <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="E33" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -5064,13 +4887,13 @@
         <v>0</v>
       </c>
       <c r="AN33" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="AO33" t="s">
         <v>84</v>
       </c>
       <c r="AQ33" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:43">
@@ -5084,10 +4907,10 @@
         <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="E34" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -5192,13 +5015,13 @@
         <v>0</v>
       </c>
       <c r="AN34" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="AO34" t="s">
         <v>84</v>
       </c>
       <c r="AQ34" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:43">
@@ -5212,10 +5035,10 @@
         <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="E35" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -5320,13 +5143,13 @@
         <v>0</v>
       </c>
       <c r="AN35" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="AO35" t="s">
         <v>84</v>
       </c>
       <c r="AQ35" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:43">
@@ -5340,10 +5163,10 @@
         <v>5</v>
       </c>
       <c r="D36" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="E36" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -5448,16 +5271,16 @@
         <v>0</v>
       </c>
       <c r="AN36" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="AO36" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="AP36">
         <v>714</v>
       </c>
       <c r="AQ36" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="1:43">
@@ -5471,10 +5294,10 @@
         <v>5</v>
       </c>
       <c r="D37" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E37" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -5579,13 +5402,13 @@
         <v>0</v>
       </c>
       <c r="AN37" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="AO37" t="s">
         <v>84</v>
       </c>
       <c r="AQ37" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
     </row>
     <row r="38" spans="1:43">
@@ -5599,10 +5422,10 @@
         <v>5</v>
       </c>
       <c r="D38" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E38" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -5707,13 +5530,13 @@
         <v>0</v>
       </c>
       <c r="AN38" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="AO38" t="s">
         <v>84</v>
       </c>
       <c r="AQ38" t="s">
-        <v>163</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" spans="1:43">
@@ -5727,10 +5550,10 @@
         <v>5</v>
       </c>
       <c r="D39" t="s">
-        <v>85</v>
+        <v>131</v>
       </c>
       <c r="E39" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -5844,7 +5667,7 @@
         <v>813</v>
       </c>
       <c r="AQ39" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40" spans="1:43">
@@ -5858,10 +5681,10 @@
         <v>5</v>
       </c>
       <c r="D40" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="E40" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -5966,16 +5789,16 @@
         <v>0</v>
       </c>
       <c r="AN40" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="AO40" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="AP40">
         <v>96</v>
       </c>
       <c r="AQ40" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="1:43">
@@ -5989,10 +5812,10 @@
         <v>7</v>
       </c>
       <c r="D41" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="E41" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -6097,13 +5920,13 @@
         <v>0</v>
       </c>
       <c r="AN41" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="AO41" t="s">
         <v>84</v>
       </c>
       <c r="AQ41" t="s">
-        <v>174</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:43">
@@ -6117,10 +5940,10 @@
         <v>8</v>
       </c>
       <c r="D42" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="E42" t="s">
-        <v>176</v>
+        <v>141</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -6225,13 +6048,13 @@
         <v>0</v>
       </c>
       <c r="AN42" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="AO42" t="s">
         <v>84</v>
       </c>
       <c r="AQ42" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" spans="1:43">
@@ -6245,10 +6068,10 @@
         <v>7</v>
       </c>
       <c r="D43" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="E43" t="s">
-        <v>180</v>
+        <v>144</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -6353,7 +6176,7 @@
         <v>0</v>
       </c>
       <c r="AN43" t="s">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="AO43" t="s">
         <v>84</v>
@@ -6362,7 +6185,7 @@
         <v>128</v>
       </c>
       <c r="AQ43" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
     </row>
     <row r="44" spans="1:43">
@@ -6376,10 +6199,10 @@
         <v>6</v>
       </c>
       <c r="D44" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="E44" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -6484,13 +6307,13 @@
         <v>0</v>
       </c>
       <c r="AN44" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="AO44" t="s">
         <v>84</v>
       </c>
       <c r="AQ44" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
     </row>
     <row r="45" spans="1:43">
@@ -6504,10 +6327,10 @@
         <v>6</v>
       </c>
       <c r="D45" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="E45" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -6612,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="AN45" t="s">
-        <v>186</v>
+        <v>148</v>
       </c>
       <c r="AO45">
         <v>-1</v>
       </c>
       <c r="AQ45" t="s">
-        <v>187</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46" spans="1:43">
@@ -6632,10 +6455,10 @@
         <v>6</v>
       </c>
       <c r="D46" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="E46" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -6740,13 +6563,13 @@
         <v>0</v>
       </c>
       <c r="AN46" t="s">
-        <v>188</v>
+        <v>149</v>
       </c>
       <c r="AO46">
         <v>-1</v>
       </c>
       <c r="AQ46" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" spans="1:43">
@@ -6760,10 +6583,10 @@
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="E47" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -6868,13 +6691,13 @@
         <v>0</v>
       </c>
       <c r="AN47" t="s">
-        <v>188</v>
+        <v>149</v>
       </c>
       <c r="AO47">
         <v>-1</v>
       </c>
       <c r="AQ47" t="s">
-        <v>190</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48" spans="1:43">
@@ -6888,10 +6711,10 @@
         <v>6</v>
       </c>
       <c r="D48" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="E48" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -6996,13 +6819,13 @@
         <v>0</v>
       </c>
       <c r="AN48" t="s">
-        <v>186</v>
+        <v>148</v>
       </c>
       <c r="AO48">
         <v>-1</v>
       </c>
       <c r="AQ48" t="s">
-        <v>191</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" spans="1:43">
@@ -7016,10 +6839,10 @@
         <v>6</v>
       </c>
       <c r="D49" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="E49" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -7124,13 +6947,13 @@
         <v>0</v>
       </c>
       <c r="AN49" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="AO49">
         <v>-1</v>
       </c>
       <c r="AQ49" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:43">
@@ -7144,10 +6967,10 @@
         <v>6</v>
       </c>
       <c r="D50" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="E50" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -7252,13 +7075,13 @@
         <v>0</v>
       </c>
       <c r="AN50" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="AO50">
         <v>-1</v>
       </c>
       <c r="AQ50" t="s">
-        <v>193</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:43">
@@ -7272,10 +7095,10 @@
         <v>6</v>
       </c>
       <c r="D51" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="E51" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -7380,13 +7203,13 @@
         <v>0</v>
       </c>
       <c r="AN51" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="AO51">
         <v>-1</v>
       </c>
       <c r="AQ51" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="1:43">
@@ -7400,10 +7223,10 @@
         <v>6</v>
       </c>
       <c r="D52" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="E52" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -7508,13 +7331,13 @@
         <v>0</v>
       </c>
       <c r="AN52" t="s">
-        <v>188</v>
+        <v>149</v>
       </c>
       <c r="AO52">
         <v>-1</v>
       </c>
       <c r="AQ52" t="s">
-        <v>195</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:43">
@@ -7528,10 +7351,10 @@
         <v>6</v>
       </c>
       <c r="D53" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="E53" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -7636,13 +7459,13 @@
         <v>0</v>
       </c>
       <c r="AN53" t="s">
-        <v>186</v>
+        <v>148</v>
       </c>
       <c r="AO53">
         <v>-1</v>
       </c>
       <c r="AQ53" t="s">
-        <v>196</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="1:43">
@@ -7656,10 +7479,10 @@
         <v>6</v>
       </c>
       <c r="D54" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="E54" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -7764,13 +7587,13 @@
         <v>0</v>
       </c>
       <c r="AN54" t="s">
-        <v>198</v>
+        <v>151</v>
       </c>
       <c r="AO54">
         <v>-1</v>
       </c>
       <c r="AQ54" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:43">
@@ -7784,10 +7607,10 @@
         <v>6</v>
       </c>
       <c r="D55" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="E55" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -7892,13 +7715,13 @@
         <v>0</v>
       </c>
       <c r="AN55" t="s">
-        <v>200</v>
+        <v>152</v>
       </c>
       <c r="AO55">
         <v>-1</v>
       </c>
       <c r="AQ55" t="s">
-        <v>201</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" spans="1:43">
@@ -7912,10 +7735,10 @@
         <v>6</v>
       </c>
       <c r="D56" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="E56" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -8020,13 +7843,13 @@
         <v>0</v>
       </c>
       <c r="AN56" t="s">
-        <v>202</v>
+        <v>153</v>
       </c>
       <c r="AO56">
         <v>-1</v>
       </c>
       <c r="AQ56" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:43">
@@ -8040,10 +7863,10 @@
         <v>6</v>
       </c>
       <c r="D57" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="E57" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -8148,13 +7971,13 @@
         <v>0</v>
       </c>
       <c r="AN57" t="s">
-        <v>204</v>
+        <v>154</v>
       </c>
       <c r="AO57">
         <v>-1</v>
       </c>
       <c r="AQ57" t="s">
-        <v>205</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58" spans="1:43">
@@ -8168,10 +7991,10 @@
         <v>6</v>
       </c>
       <c r="D58" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="E58" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -8276,13 +8099,13 @@
         <v>0</v>
       </c>
       <c r="AN58" t="s">
-        <v>200</v>
+        <v>152</v>
       </c>
       <c r="AO58">
         <v>-1</v>
       </c>
       <c r="AQ58" t="s">
-        <v>206</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" spans="1:43">
@@ -8296,10 +8119,10 @@
         <v>6</v>
       </c>
       <c r="D59" t="s">
-        <v>207</v>
+        <v>155</v>
       </c>
       <c r="E59" t="s">
-        <v>207</v>
+        <v>155</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -8404,13 +8227,13 @@
         <v>0</v>
       </c>
       <c r="AN59" t="s">
-        <v>202</v>
+        <v>153</v>
       </c>
       <c r="AO59">
         <v>-1</v>
       </c>
       <c r="AQ59" t="s">
-        <v>208</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60" spans="1:43">
@@ -8424,10 +8247,10 @@
         <v>6</v>
       </c>
       <c r="D60" t="s">
-        <v>209</v>
+        <v>156</v>
       </c>
       <c r="E60" t="s">
-        <v>209</v>
+        <v>156</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -8532,13 +8355,13 @@
         <v>0</v>
       </c>
       <c r="AN60" t="s">
-        <v>210</v>
+        <v>157</v>
       </c>
       <c r="AO60">
         <v>-1</v>
       </c>
       <c r="AQ60" t="s">
-        <v>211</v>
+        <v>156</v>
       </c>
     </row>
     <row r="61" spans="1:43">
@@ -8552,10 +8375,10 @@
         <v>6</v>
       </c>
       <c r="D61" t="s">
-        <v>209</v>
+        <v>156</v>
       </c>
       <c r="E61" t="s">
-        <v>209</v>
+        <v>156</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -8660,13 +8483,13 @@
         <v>0</v>
       </c>
       <c r="AN61" t="s">
-        <v>210</v>
+        <v>157</v>
       </c>
       <c r="AO61">
         <v>-1</v>
       </c>
       <c r="AQ61" t="s">
-        <v>212</v>
+        <v>156</v>
       </c>
     </row>
     <row r="62" spans="1:43">
@@ -8680,10 +8503,10 @@
         <v>6</v>
       </c>
       <c r="D62" t="s">
-        <v>209</v>
+        <v>156</v>
       </c>
       <c r="E62" t="s">
-        <v>209</v>
+        <v>156</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -8788,13 +8611,13 @@
         <v>0</v>
       </c>
       <c r="AN62" t="s">
-        <v>210</v>
+        <v>157</v>
       </c>
       <c r="AO62">
         <v>-1</v>
       </c>
       <c r="AQ62" t="s">
-        <v>213</v>
+        <v>156</v>
       </c>
     </row>
     <row r="63" spans="1:43">
@@ -8808,10 +8631,10 @@
         <v>6</v>
       </c>
       <c r="D63" t="s">
-        <v>209</v>
+        <v>156</v>
       </c>
       <c r="E63" t="s">
-        <v>209</v>
+        <v>156</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -8916,13 +8739,13 @@
         <v>0</v>
       </c>
       <c r="AN63" t="s">
-        <v>210</v>
+        <v>157</v>
       </c>
       <c r="AO63">
         <v>-1</v>
       </c>
       <c r="AQ63" t="s">
-        <v>214</v>
+        <v>156</v>
       </c>
     </row>
     <row r="64" spans="1:43">
@@ -8936,10 +8759,10 @@
         <v>6</v>
       </c>
       <c r="D64" t="s">
-        <v>209</v>
+        <v>156</v>
       </c>
       <c r="E64" t="s">
-        <v>209</v>
+        <v>156</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -9044,13 +8867,13 @@
         <v>0</v>
       </c>
       <c r="AN64" t="s">
-        <v>210</v>
+        <v>157</v>
       </c>
       <c r="AO64">
         <v>-1</v>
       </c>
       <c r="AQ64" t="s">
-        <v>215</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65" spans="1:43">
@@ -9064,10 +8887,10 @@
         <v>4</v>
       </c>
       <c r="D65" t="s">
-        <v>216</v>
+        <v>158</v>
       </c>
       <c r="E65" t="s">
-        <v>216</v>
+        <v>158</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -9172,13 +8995,13 @@
         <v>0</v>
       </c>
       <c r="AN65" t="s">
-        <v>217</v>
+        <v>159</v>
       </c>
       <c r="AO65" t="s">
         <v>84</v>
       </c>
       <c r="AQ65" t="s">
-        <v>218</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/jyx2/Assets/Mods/shendiao/Configs/人物.xlsx
+++ b/jyx2/Assets/Mods/shendiao/Configs/人物.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
   <si>
     <t>LuaConfigGen</t>
   </si>
@@ -494,18 +494,33 @@
   </si>
   <si>
     <t>42,700</t>
+  </si>
+  <si>
+    <t>丘处机</t>
+  </si>
+  <si>
+    <t>23,900</t>
+  </si>
+  <si>
+    <t>神雕</t>
+  </si>
+  <si>
+    <t>40,600</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -536,12 +551,12 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -825,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ65"/>
+  <dimension ref="A1:AQ67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:43">
@@ -9002,6 +9017,265 @@
       </c>
       <c r="AQ65" t="s">
         <v>158</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>23</v>
+      </c>
+      <c r="B66">
+        <v>23</v>
+      </c>
+      <c r="C66">
+        <v>10</v>
+      </c>
+      <c r="D66" t="s">
+        <v>160</v>
+      </c>
+      <c r="E66" t="s">
+        <v>160</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>40</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>999</v>
+      </c>
+      <c r="J66">
+        <v>999</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>90</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>-1</v>
+      </c>
+      <c r="P66">
+        <v>-1</v>
+      </c>
+      <c r="Q66">
+        <v>2</v>
+      </c>
+      <c r="R66">
+        <v>999</v>
+      </c>
+      <c r="S66">
+        <v>999</v>
+      </c>
+      <c r="T66">
+        <v>95</v>
+      </c>
+      <c r="U66">
+        <v>80</v>
+      </c>
+      <c r="V66">
+        <v>95</v>
+      </c>
+      <c r="W66">
+        <v>10</v>
+      </c>
+      <c r="X66">
+        <v>10</v>
+      </c>
+      <c r="Y66">
+        <v>10</v>
+      </c>
+      <c r="Z66">
+        <v>10</v>
+      </c>
+      <c r="AA66">
+        <v>90</v>
+      </c>
+      <c r="AB66">
+        <v>90</v>
+      </c>
+      <c r="AC66">
+        <v>10</v>
+      </c>
+      <c r="AD66">
+        <v>10</v>
+      </c>
+      <c r="AE66">
+        <v>10</v>
+      </c>
+      <c r="AF66">
+        <v>95</v>
+      </c>
+      <c r="AG66">
+        <v>90</v>
+      </c>
+      <c r="AH66">
+        <v>0</v>
+      </c>
+      <c r="AI66">
+        <v>0</v>
+      </c>
+      <c r="AJ66">
+        <v>0</v>
+      </c>
+      <c r="AK66">
+        <v>85</v>
+      </c>
+      <c r="AL66">
+        <v>-1</v>
+      </c>
+      <c r="AM66">
+        <v>0</v>
+      </c>
+      <c r="AN66" t="s">
+        <v>161</v>
+      </c>
+      <c r="AO66">
+        <v>-1</v>
+      </c>
+      <c r="AQ66" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>24</v>
+      </c>
+      <c r="B67">
+        <v>24</v>
+      </c>
+      <c r="C67">
+        <v>20</v>
+      </c>
+      <c r="D67" t="s">
+        <v>162</v>
+      </c>
+      <c r="E67" t="s">
+        <v>162</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>32</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>4000</v>
+      </c>
+      <c r="J67">
+        <v>4000</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>100</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>-1</v>
+      </c>
+      <c r="P67">
+        <v>-1</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>400</v>
+      </c>
+      <c r="S67">
+        <v>400</v>
+      </c>
+      <c r="T67">
+        <v>160</v>
+      </c>
+      <c r="U67">
+        <v>110</v>
+      </c>
+      <c r="V67">
+        <v>130</v>
+      </c>
+      <c r="W67">
+        <v>0</v>
+      </c>
+      <c r="X67">
+        <v>0</v>
+      </c>
+      <c r="Y67">
+        <v>0</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+      <c r="AA67">
+        <v>150</v>
+      </c>
+      <c r="AB67">
+        <v>80</v>
+      </c>
+      <c r="AC67">
+        <v>0</v>
+      </c>
+      <c r="AD67">
+        <v>0</v>
+      </c>
+      <c r="AE67">
+        <v>0</v>
+      </c>
+      <c r="AF67">
+        <v>60</v>
+      </c>
+      <c r="AG67">
+        <v>50</v>
+      </c>
+      <c r="AH67">
+        <v>0</v>
+      </c>
+      <c r="AI67">
+        <v>0</v>
+      </c>
+      <c r="AJ67">
+        <v>0</v>
+      </c>
+      <c r="AK67">
+        <v>50</v>
+      </c>
+      <c r="AL67">
+        <v>-1</v>
+      </c>
+      <c r="AM67">
+        <v>0</v>
+      </c>
+      <c r="AN67" t="s">
+        <v>163</v>
+      </c>
+      <c r="AO67" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP67" t="s">
+        <v>164</v>
+      </c>
+      <c r="AQ67" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/jyx2/Assets/Mods/shendiao/Configs/人物.xlsx
+++ b/jyx2/Assets/Mods/shendiao/Configs/人物.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
   <si>
     <t>LuaConfigGen</t>
   </si>
@@ -509,6 +509,42 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>公孙止</t>
+  </si>
+  <si>
+    <t>绝情谷主</t>
+  </si>
+  <si>
+    <t>60,400</t>
+  </si>
+  <si>
+    <t>公孙绿萼</t>
+  </si>
+  <si>
+    <t>公孙姑娘</t>
+  </si>
+  <si>
+    <t>0,300</t>
+  </si>
+  <si>
+    <t>樊一翁</t>
+  </si>
+  <si>
+    <t>长须鬼</t>
+  </si>
+  <si>
+    <t>90,350</t>
+  </si>
+  <si>
+    <t>裘千尺</t>
+  </si>
+  <si>
+    <t>铁掌莲花</t>
+  </si>
+  <si>
+    <t>97,500</t>
   </si>
 </sst>
 </file>
@@ -840,7 +876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ67"/>
+  <dimension ref="A1:AQ71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:43">
@@ -9276,6 +9312,530 @@
       </c>
       <c r="AQ67" t="s">
         <v>162</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>26</v>
+      </c>
+      <c r="B68">
+        <v>26</v>
+      </c>
+      <c r="C68">
+        <v>10</v>
+      </c>
+      <c r="D68" t="s">
+        <v>165</v>
+      </c>
+      <c r="E68" t="s">
+        <v>166</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>42</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>2600</v>
+      </c>
+      <c r="J68">
+        <v>2600</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>90</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>-1</v>
+      </c>
+      <c r="P68">
+        <v>-1</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>400</v>
+      </c>
+      <c r="S68">
+        <v>400</v>
+      </c>
+      <c r="T68">
+        <v>105</v>
+      </c>
+      <c r="U68">
+        <v>60</v>
+      </c>
+      <c r="V68">
+        <v>95</v>
+      </c>
+      <c r="W68">
+        <v>20</v>
+      </c>
+      <c r="X68">
+        <v>0</v>
+      </c>
+      <c r="Y68">
+        <v>0</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+      <c r="AA68">
+        <v>95</v>
+      </c>
+      <c r="AB68">
+        <v>85</v>
+      </c>
+      <c r="AC68">
+        <v>10</v>
+      </c>
+      <c r="AD68">
+        <v>10</v>
+      </c>
+      <c r="AE68">
+        <v>10</v>
+      </c>
+      <c r="AF68">
+        <v>70</v>
+      </c>
+      <c r="AG68">
+        <v>30</v>
+      </c>
+      <c r="AH68">
+        <v>0</v>
+      </c>
+      <c r="AI68">
+        <v>0</v>
+      </c>
+      <c r="AJ68">
+        <v>0</v>
+      </c>
+      <c r="AK68">
+        <v>70</v>
+      </c>
+      <c r="AL68">
+        <v>-1</v>
+      </c>
+      <c r="AM68">
+        <v>0</v>
+      </c>
+      <c r="AN68" t="s">
+        <v>167</v>
+      </c>
+      <c r="AO68" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP68" t="s">
+        <v>164</v>
+      </c>
+      <c r="AQ68" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>27</v>
+      </c>
+      <c r="B69">
+        <v>27</v>
+      </c>
+      <c r="C69">
+        <v>8</v>
+      </c>
+      <c r="D69" t="s">
+        <v>168</v>
+      </c>
+      <c r="E69" t="s">
+        <v>169</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="G69">
+        <v>26</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>620</v>
+      </c>
+      <c r="J69">
+        <v>620</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>80</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>-1</v>
+      </c>
+      <c r="P69">
+        <v>-1</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>200</v>
+      </c>
+      <c r="S69">
+        <v>200</v>
+      </c>
+      <c r="T69">
+        <v>62</v>
+      </c>
+      <c r="U69">
+        <v>55</v>
+      </c>
+      <c r="V69">
+        <v>50</v>
+      </c>
+      <c r="W69">
+        <v>30</v>
+      </c>
+      <c r="X69">
+        <v>0</v>
+      </c>
+      <c r="Y69">
+        <v>0</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+      <c r="AA69">
+        <v>60</v>
+      </c>
+      <c r="AB69">
+        <v>55</v>
+      </c>
+      <c r="AC69">
+        <v>10</v>
+      </c>
+      <c r="AD69">
+        <v>10</v>
+      </c>
+      <c r="AE69">
+        <v>10</v>
+      </c>
+      <c r="AF69">
+        <v>40</v>
+      </c>
+      <c r="AG69">
+        <v>70</v>
+      </c>
+      <c r="AH69">
+        <v>0</v>
+      </c>
+      <c r="AI69">
+        <v>0</v>
+      </c>
+      <c r="AJ69">
+        <v>0</v>
+      </c>
+      <c r="AK69">
+        <v>65</v>
+      </c>
+      <c r="AL69">
+        <v>-1</v>
+      </c>
+      <c r="AM69">
+        <v>0</v>
+      </c>
+      <c r="AN69" t="s">
+        <v>170</v>
+      </c>
+      <c r="AO69" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP69" t="s">
+        <v>164</v>
+      </c>
+      <c r="AQ69" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>28</v>
+      </c>
+      <c r="B70">
+        <v>28</v>
+      </c>
+      <c r="C70">
+        <v>9</v>
+      </c>
+      <c r="D70" t="s">
+        <v>171</v>
+      </c>
+      <c r="E70" t="s">
+        <v>172</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>35</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>1300</v>
+      </c>
+      <c r="J70">
+        <v>1300</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>85</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>-1</v>
+      </c>
+      <c r="P70">
+        <v>-1</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <v>250</v>
+      </c>
+      <c r="S70">
+        <v>250</v>
+      </c>
+      <c r="T70">
+        <v>85</v>
+      </c>
+      <c r="U70">
+        <v>50</v>
+      </c>
+      <c r="V70">
+        <v>75</v>
+      </c>
+      <c r="W70">
+        <v>0</v>
+      </c>
+      <c r="X70">
+        <v>0</v>
+      </c>
+      <c r="Y70">
+        <v>0</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+      <c r="AA70">
+        <v>70</v>
+      </c>
+      <c r="AB70">
+        <v>40</v>
+      </c>
+      <c r="AC70">
+        <v>30</v>
+      </c>
+      <c r="AD70">
+        <v>10</v>
+      </c>
+      <c r="AE70">
+        <v>10</v>
+      </c>
+      <c r="AF70">
+        <v>55</v>
+      </c>
+      <c r="AG70">
+        <v>55</v>
+      </c>
+      <c r="AH70">
+        <v>0</v>
+      </c>
+      <c r="AI70">
+        <v>0</v>
+      </c>
+      <c r="AJ70">
+        <v>0</v>
+      </c>
+      <c r="AK70">
+        <v>55</v>
+      </c>
+      <c r="AL70">
+        <v>-1</v>
+      </c>
+      <c r="AM70">
+        <v>0</v>
+      </c>
+      <c r="AN70" t="s">
+        <v>173</v>
+      </c>
+      <c r="AO70" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP70" t="s">
+        <v>164</v>
+      </c>
+      <c r="AQ70" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>29</v>
+      </c>
+      <c r="B71">
+        <v>29</v>
+      </c>
+      <c r="C71">
+        <v>5</v>
+      </c>
+      <c r="D71" t="s">
+        <v>174</v>
+      </c>
+      <c r="E71" t="s">
+        <v>175</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71">
+        <v>40</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>900</v>
+      </c>
+      <c r="J71">
+        <v>900</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>60</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>-1</v>
+      </c>
+      <c r="P71">
+        <v>-1</v>
+      </c>
+      <c r="Q71">
+        <v>1</v>
+      </c>
+      <c r="R71">
+        <v>600</v>
+      </c>
+      <c r="S71">
+        <v>600</v>
+      </c>
+      <c r="T71">
+        <v>95</v>
+      </c>
+      <c r="U71">
+        <v>30</v>
+      </c>
+      <c r="V71">
+        <v>60</v>
+      </c>
+      <c r="W71">
+        <v>10</v>
+      </c>
+      <c r="X71">
+        <v>0</v>
+      </c>
+      <c r="Y71">
+        <v>0</v>
+      </c>
+      <c r="Z71">
+        <v>20</v>
+      </c>
+      <c r="AA71">
+        <v>40</v>
+      </c>
+      <c r="AB71">
+        <v>40</v>
+      </c>
+      <c r="AC71">
+        <v>10</v>
+      </c>
+      <c r="AD71">
+        <v>10</v>
+      </c>
+      <c r="AE71">
+        <v>90</v>
+      </c>
+      <c r="AF71">
+        <v>75</v>
+      </c>
+      <c r="AG71">
+        <v>40</v>
+      </c>
+      <c r="AH71">
+        <v>0</v>
+      </c>
+      <c r="AI71">
+        <v>0</v>
+      </c>
+      <c r="AJ71">
+        <v>0</v>
+      </c>
+      <c r="AK71">
+        <v>80</v>
+      </c>
+      <c r="AL71">
+        <v>-1</v>
+      </c>
+      <c r="AM71">
+        <v>0</v>
+      </c>
+      <c r="AN71" t="s">
+        <v>176</v>
+      </c>
+      <c r="AO71" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP71" t="s">
+        <v>164</v>
+      </c>
+      <c r="AQ71" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/jyx2/Assets/Mods/shendiao/Configs/人物.xlsx
+++ b/jyx2/Assets/Mods/shendiao/Configs/人物.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
   <si>
     <t>LuaConfigGen</t>
   </si>
@@ -545,6 +545,48 @@
   </si>
   <si>
     <t>97,500</t>
+  </si>
+  <si>
+    <t>陆无双</t>
+  </si>
+  <si>
+    <t>无双姑娘</t>
+  </si>
+  <si>
+    <t>181,300</t>
+  </si>
+  <si>
+    <t>周伯通</t>
+  </si>
+  <si>
+    <t>老顽童</t>
+  </si>
+  <si>
+    <t>30,900</t>
+  </si>
+  <si>
+    <t>瑛姑</t>
+  </si>
+  <si>
+    <t>黑泥沼主</t>
+  </si>
+  <si>
+    <t>一灯</t>
+  </si>
+  <si>
+    <t>一灯大师</t>
+  </si>
+  <si>
+    <t>61,900</t>
+  </si>
+  <si>
+    <t>裘千仞</t>
+  </si>
+  <si>
+    <t>铁掌帮帮主</t>
+  </si>
+  <si>
+    <t>62,700</t>
   </si>
 </sst>
 </file>
@@ -876,7 +918,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ71"/>
+  <dimension ref="A1:AQ76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:43">
@@ -9836,6 +9878,661 @@
       </c>
       <c r="AQ71" t="s">
         <v>174</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>35</v>
+      </c>
+      <c r="B72">
+        <v>35</v>
+      </c>
+      <c r="C72">
+        <v>7</v>
+      </c>
+      <c r="D72" t="s">
+        <v>177</v>
+      </c>
+      <c r="E72" t="s">
+        <v>178</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72">
+        <v>24</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>560</v>
+      </c>
+      <c r="J72">
+        <v>560</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>85</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>-1</v>
+      </c>
+      <c r="P72">
+        <v>-1</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>180</v>
+      </c>
+      <c r="S72">
+        <v>180</v>
+      </c>
+      <c r="T72">
+        <v>60</v>
+      </c>
+      <c r="U72">
+        <v>60</v>
+      </c>
+      <c r="V72">
+        <v>48</v>
+      </c>
+      <c r="W72">
+        <v>20</v>
+      </c>
+      <c r="X72">
+        <v>0</v>
+      </c>
+      <c r="Y72">
+        <v>0</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+      <c r="AA72">
+        <v>55</v>
+      </c>
+      <c r="AB72">
+        <v>50</v>
+      </c>
+      <c r="AC72">
+        <v>55</v>
+      </c>
+      <c r="AD72">
+        <v>10</v>
+      </c>
+      <c r="AE72">
+        <v>10</v>
+      </c>
+      <c r="AF72">
+        <v>45</v>
+      </c>
+      <c r="AG72">
+        <v>60</v>
+      </c>
+      <c r="AH72">
+        <v>0</v>
+      </c>
+      <c r="AI72">
+        <v>0</v>
+      </c>
+      <c r="AJ72">
+        <v>0</v>
+      </c>
+      <c r="AK72">
+        <v>60</v>
+      </c>
+      <c r="AL72">
+        <v>-1</v>
+      </c>
+      <c r="AM72">
+        <v>0</v>
+      </c>
+      <c r="AN72" t="s">
+        <v>179</v>
+      </c>
+      <c r="AO72" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP72" t="s">
+        <v>164</v>
+      </c>
+      <c r="AQ72" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>36</v>
+      </c>
+      <c r="B73">
+        <v>36</v>
+      </c>
+      <c r="C73">
+        <v>15</v>
+      </c>
+      <c r="D73" t="s">
+        <v>180</v>
+      </c>
+      <c r="E73" t="s">
+        <v>181</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>65</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>3000</v>
+      </c>
+      <c r="J73">
+        <v>3000</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>100</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>-1</v>
+      </c>
+      <c r="P73">
+        <v>-1</v>
+      </c>
+      <c r="Q73">
+        <v>2</v>
+      </c>
+      <c r="R73">
+        <v>900</v>
+      </c>
+      <c r="S73">
+        <v>900</v>
+      </c>
+      <c r="T73">
+        <v>150</v>
+      </c>
+      <c r="U73">
+        <v>130</v>
+      </c>
+      <c r="V73">
+        <v>130</v>
+      </c>
+      <c r="W73">
+        <v>10</v>
+      </c>
+      <c r="X73">
+        <v>0</v>
+      </c>
+      <c r="Y73">
+        <v>0</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+      <c r="AA73">
+        <v>150</v>
+      </c>
+      <c r="AB73">
+        <v>40</v>
+      </c>
+      <c r="AC73">
+        <v>10</v>
+      </c>
+      <c r="AD73">
+        <v>10</v>
+      </c>
+      <c r="AE73">
+        <v>10</v>
+      </c>
+      <c r="AF73">
+        <v>90</v>
+      </c>
+      <c r="AG73">
+        <v>60</v>
+      </c>
+      <c r="AH73">
+        <v>0</v>
+      </c>
+      <c r="AI73">
+        <v>1</v>
+      </c>
+      <c r="AJ73">
+        <v>0</v>
+      </c>
+      <c r="AK73">
+        <v>60</v>
+      </c>
+      <c r="AL73">
+        <v>-1</v>
+      </c>
+      <c r="AM73">
+        <v>0</v>
+      </c>
+      <c r="AN73" t="s">
+        <v>182</v>
+      </c>
+      <c r="AO73" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP73" t="s">
+        <v>164</v>
+      </c>
+      <c r="AQ73" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>37</v>
+      </c>
+      <c r="B74">
+        <v>37</v>
+      </c>
+      <c r="C74">
+        <v>6</v>
+      </c>
+      <c r="D74" t="s">
+        <v>183</v>
+      </c>
+      <c r="E74" t="s">
+        <v>184</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="G74">
+        <v>50</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>1600</v>
+      </c>
+      <c r="J74">
+        <v>1600</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>80</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>-1</v>
+      </c>
+      <c r="P74">
+        <v>-1</v>
+      </c>
+      <c r="Q74">
+        <v>1</v>
+      </c>
+      <c r="R74">
+        <v>500</v>
+      </c>
+      <c r="S74">
+        <v>500</v>
+      </c>
+      <c r="T74">
+        <v>100</v>
+      </c>
+      <c r="U74">
+        <v>90</v>
+      </c>
+      <c r="V74">
+        <v>80</v>
+      </c>
+      <c r="W74">
+        <v>30</v>
+      </c>
+      <c r="X74">
+        <v>20</v>
+      </c>
+      <c r="Y74">
+        <v>10</v>
+      </c>
+      <c r="Z74">
+        <v>20</v>
+      </c>
+      <c r="AA74">
+        <v>40</v>
+      </c>
+      <c r="AB74">
+        <v>40</v>
+      </c>
+      <c r="AC74">
+        <v>10</v>
+      </c>
+      <c r="AD74">
+        <v>10</v>
+      </c>
+      <c r="AE74">
+        <v>90</v>
+      </c>
+      <c r="AF74">
+        <v>70</v>
+      </c>
+      <c r="AG74">
+        <v>40</v>
+      </c>
+      <c r="AH74">
+        <v>0</v>
+      </c>
+      <c r="AI74">
+        <v>0</v>
+      </c>
+      <c r="AJ74">
+        <v>0</v>
+      </c>
+      <c r="AK74">
+        <v>70</v>
+      </c>
+      <c r="AL74">
+        <v>-1</v>
+      </c>
+      <c r="AM74">
+        <v>0</v>
+      </c>
+      <c r="AN74" t="s">
+        <v>176</v>
+      </c>
+      <c r="AO74" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP74" t="s">
+        <v>164</v>
+      </c>
+      <c r="AQ74" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>38</v>
+      </c>
+      <c r="B75">
+        <v>38</v>
+      </c>
+      <c r="C75">
+        <v>12</v>
+      </c>
+      <c r="D75" t="s">
+        <v>185</v>
+      </c>
+      <c r="E75" t="s">
+        <v>186</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>70</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>4000</v>
+      </c>
+      <c r="J75">
+        <v>4000</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>100</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>-1</v>
+      </c>
+      <c r="P75">
+        <v>-1</v>
+      </c>
+      <c r="Q75">
+        <v>2</v>
+      </c>
+      <c r="R75">
+        <v>1200</v>
+      </c>
+      <c r="S75">
+        <v>1200</v>
+      </c>
+      <c r="T75">
+        <v>140</v>
+      </c>
+      <c r="U75">
+        <v>100</v>
+      </c>
+      <c r="V75">
+        <v>150</v>
+      </c>
+      <c r="W75">
+        <v>100</v>
+      </c>
+      <c r="X75">
+        <v>0</v>
+      </c>
+      <c r="Y75">
+        <v>60</v>
+      </c>
+      <c r="Z75">
+        <v>40</v>
+      </c>
+      <c r="AA75">
+        <v>140</v>
+      </c>
+      <c r="AB75">
+        <v>100</v>
+      </c>
+      <c r="AC75">
+        <v>10</v>
+      </c>
+      <c r="AD75">
+        <v>10</v>
+      </c>
+      <c r="AE75">
+        <v>30</v>
+      </c>
+      <c r="AF75">
+        <v>90</v>
+      </c>
+      <c r="AG75">
+        <v>90</v>
+      </c>
+      <c r="AH75">
+        <v>0</v>
+      </c>
+      <c r="AI75">
+        <v>0</v>
+      </c>
+      <c r="AJ75">
+        <v>0</v>
+      </c>
+      <c r="AK75">
+        <v>85</v>
+      </c>
+      <c r="AL75">
+        <v>-1</v>
+      </c>
+      <c r="AM75">
+        <v>0</v>
+      </c>
+      <c r="AN75" t="s">
+        <v>187</v>
+      </c>
+      <c r="AO75" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP75" t="s">
+        <v>164</v>
+      </c>
+      <c r="AQ75" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>39</v>
+      </c>
+      <c r="B76">
+        <v>39</v>
+      </c>
+      <c r="C76">
+        <v>11</v>
+      </c>
+      <c r="D76" t="s">
+        <v>188</v>
+      </c>
+      <c r="E76" t="s">
+        <v>189</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>52</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>2800</v>
+      </c>
+      <c r="J76">
+        <v>2800</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>95</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>-1</v>
+      </c>
+      <c r="P76">
+        <v>-1</v>
+      </c>
+      <c r="Q76">
+        <v>1</v>
+      </c>
+      <c r="R76">
+        <v>700</v>
+      </c>
+      <c r="S76">
+        <v>700</v>
+      </c>
+      <c r="T76">
+        <v>125</v>
+      </c>
+      <c r="U76">
+        <v>85</v>
+      </c>
+      <c r="V76">
+        <v>110</v>
+      </c>
+      <c r="W76">
+        <v>10</v>
+      </c>
+      <c r="X76">
+        <v>0</v>
+      </c>
+      <c r="Y76">
+        <v>0</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+      <c r="AA76">
+        <v>120</v>
+      </c>
+      <c r="AB76">
+        <v>40</v>
+      </c>
+      <c r="AC76">
+        <v>20</v>
+      </c>
+      <c r="AD76">
+        <v>10</v>
+      </c>
+      <c r="AE76">
+        <v>10</v>
+      </c>
+      <c r="AF76">
+        <v>70</v>
+      </c>
+      <c r="AG76">
+        <v>25</v>
+      </c>
+      <c r="AH76">
+        <v>0</v>
+      </c>
+      <c r="AI76">
+        <v>0</v>
+      </c>
+      <c r="AJ76">
+        <v>0</v>
+      </c>
+      <c r="AK76">
+        <v>70</v>
+      </c>
+      <c r="AL76">
+        <v>-1</v>
+      </c>
+      <c r="AM76">
+        <v>0</v>
+      </c>
+      <c r="AN76" t="s">
+        <v>190</v>
+      </c>
+      <c r="AO76" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP76" t="s">
+        <v>164</v>
+      </c>
+      <c r="AQ76" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/jyx2/Assets/Mods/shendiao/Configs/人物.xlsx
+++ b/jyx2/Assets/Mods/shendiao/Configs/人物.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
   <si>
     <t>LuaConfigGen</t>
   </si>
@@ -587,6 +587,15 @@
   </si>
   <si>
     <t>62,700</t>
+  </si>
+  <si>
+    <t>华山派弟子</t>
+  </si>
+  <si>
+    <t>华山门下</t>
+  </si>
+  <si>
+    <t>1,300</t>
   </si>
 </sst>
 </file>
@@ -918,7 +927,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ76"/>
+  <dimension ref="A1:AQ77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:43">
@@ -10533,6 +10542,137 @@
       </c>
       <c r="AQ76" t="s">
         <v>188</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>43</v>
+      </c>
+      <c r="B77">
+        <v>43</v>
+      </c>
+      <c r="C77">
+        <v>6</v>
+      </c>
+      <c r="D77" t="s">
+        <v>191</v>
+      </c>
+      <c r="E77" t="s">
+        <v>192</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>22</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>520</v>
+      </c>
+      <c r="J77">
+        <v>520</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>85</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>-1</v>
+      </c>
+      <c r="P77">
+        <v>-1</v>
+      </c>
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="R77">
+        <v>160</v>
+      </c>
+      <c r="S77">
+        <v>160</v>
+      </c>
+      <c r="T77">
+        <v>62</v>
+      </c>
+      <c r="U77">
+        <v>58</v>
+      </c>
+      <c r="V77">
+        <v>50</v>
+      </c>
+      <c r="W77">
+        <v>10</v>
+      </c>
+      <c r="X77">
+        <v>0</v>
+      </c>
+      <c r="Y77">
+        <v>0</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+      <c r="AA77">
+        <v>50</v>
+      </c>
+      <c r="AB77">
+        <v>65</v>
+      </c>
+      <c r="AC77">
+        <v>10</v>
+      </c>
+      <c r="AD77">
+        <v>10</v>
+      </c>
+      <c r="AE77">
+        <v>10</v>
+      </c>
+      <c r="AF77">
+        <v>40</v>
+      </c>
+      <c r="AG77">
+        <v>60</v>
+      </c>
+      <c r="AH77">
+        <v>0</v>
+      </c>
+      <c r="AI77">
+        <v>0</v>
+      </c>
+      <c r="AJ77">
+        <v>0</v>
+      </c>
+      <c r="AK77">
+        <v>55</v>
+      </c>
+      <c r="AL77">
+        <v>-1</v>
+      </c>
+      <c r="AM77">
+        <v>0</v>
+      </c>
+      <c r="AN77" t="s">
+        <v>193</v>
+      </c>
+      <c r="AO77" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP77" t="s">
+        <v>164</v>
+      </c>
+      <c r="AQ77" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/jyx2/Assets/Mods/shendiao/Configs/人物.xlsx
+++ b/jyx2/Assets/Mods/shendiao/Configs/人物.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
   <si>
     <t>LuaConfigGen</t>
   </si>
@@ -596,6 +596,21 @@
   </si>
   <si>
     <t>1,300</t>
+  </si>
+  <si>
+    <t>武三通</t>
+  </si>
+  <si>
+    <t>一灯门下</t>
+  </si>
+  <si>
+    <t>洪凌波</t>
+  </si>
+  <si>
+    <t>古墓门下</t>
+  </si>
+  <si>
+    <t>181,220</t>
   </si>
 </sst>
 </file>
@@ -927,7 +942,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ77"/>
+  <dimension ref="A1:AQ79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:43">
@@ -1300,16 +1315,16 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="I5">
-        <v>38</v>
+        <v>300</v>
       </c>
       <c r="J5">
-        <v>38</v>
+        <v>300</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -1336,16 +1351,16 @@
         <v>26</v>
       </c>
       <c r="S5">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="T5">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="U5">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="V5">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="W5">
         <v>30</v>
@@ -10673,6 +10688,262 @@
       </c>
       <c r="AQ77" t="s">
         <v>191</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>44</v>
+      </c>
+      <c r="B78">
+        <v>44</v>
+      </c>
+      <c r="C78">
+        <v>12</v>
+      </c>
+      <c r="D78" t="s">
+        <v>194</v>
+      </c>
+      <c r="E78" t="s">
+        <v>195</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>40</v>
+      </c>
+      <c r="H78">
+        <v>-22086</v>
+      </c>
+      <c r="I78">
+        <v>900</v>
+      </c>
+      <c r="J78">
+        <v>900</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>90</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>-1</v>
+      </c>
+      <c r="P78">
+        <v>-1</v>
+      </c>
+      <c r="Q78">
+        <v>1</v>
+      </c>
+      <c r="R78">
+        <v>900</v>
+      </c>
+      <c r="S78">
+        <v>900</v>
+      </c>
+      <c r="T78">
+        <v>110</v>
+      </c>
+      <c r="U78">
+        <v>70</v>
+      </c>
+      <c r="V78">
+        <v>105</v>
+      </c>
+      <c r="W78">
+        <v>0</v>
+      </c>
+      <c r="X78">
+        <v>0</v>
+      </c>
+      <c r="Y78">
+        <v>0</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+      <c r="AA78">
+        <v>95</v>
+      </c>
+      <c r="AB78">
+        <v>10</v>
+      </c>
+      <c r="AC78">
+        <v>10</v>
+      </c>
+      <c r="AD78">
+        <v>10</v>
+      </c>
+      <c r="AE78">
+        <v>30</v>
+      </c>
+      <c r="AF78">
+        <v>95</v>
+      </c>
+      <c r="AG78">
+        <v>80</v>
+      </c>
+      <c r="AH78">
+        <v>0</v>
+      </c>
+      <c r="AI78">
+        <v>0</v>
+      </c>
+      <c r="AJ78">
+        <v>0</v>
+      </c>
+      <c r="AK78">
+        <v>55</v>
+      </c>
+      <c r="AL78">
+        <v>-1</v>
+      </c>
+      <c r="AM78">
+        <v>0</v>
+      </c>
+      <c r="AN78" t="s">
+        <v>115</v>
+      </c>
+      <c r="AO78">
+        <v>-1</v>
+      </c>
+      <c r="AQ78" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>73</v>
+      </c>
+      <c r="B79">
+        <v>73</v>
+      </c>
+      <c r="C79">
+        <v>7</v>
+      </c>
+      <c r="D79" t="s">
+        <v>196</v>
+      </c>
+      <c r="E79" t="s">
+        <v>197</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="G79">
+        <v>22</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>480</v>
+      </c>
+      <c r="J79">
+        <v>480</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>85</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>-1</v>
+      </c>
+      <c r="P79">
+        <v>-1</v>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79">
+        <v>160</v>
+      </c>
+      <c r="S79">
+        <v>160</v>
+      </c>
+      <c r="T79">
+        <v>58</v>
+      </c>
+      <c r="U79">
+        <v>62</v>
+      </c>
+      <c r="V79">
+        <v>45</v>
+      </c>
+      <c r="W79">
+        <v>10</v>
+      </c>
+      <c r="X79">
+        <v>0</v>
+      </c>
+      <c r="Y79">
+        <v>0</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+      <c r="AA79">
+        <v>50</v>
+      </c>
+      <c r="AB79">
+        <v>40</v>
+      </c>
+      <c r="AC79">
+        <v>40</v>
+      </c>
+      <c r="AD79">
+        <v>5</v>
+      </c>
+      <c r="AE79">
+        <v>15</v>
+      </c>
+      <c r="AF79">
+        <v>40</v>
+      </c>
+      <c r="AG79">
+        <v>55</v>
+      </c>
+      <c r="AH79">
+        <v>0</v>
+      </c>
+      <c r="AI79">
+        <v>0</v>
+      </c>
+      <c r="AJ79">
+        <v>0</v>
+      </c>
+      <c r="AK79">
+        <v>62</v>
+      </c>
+      <c r="AL79">
+        <v>-1</v>
+      </c>
+      <c r="AM79">
+        <v>0</v>
+      </c>
+      <c r="AN79" t="s">
+        <v>198</v>
+      </c>
+      <c r="AO79">
+        <v>-1</v>
+      </c>
+      <c r="AQ79" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
